--- a/output/2024/sector_totals_v2.5_year2024.xlsx
+++ b/output/2024/sector_totals_v2.5_year2024.xlsx
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1568.881735365662</v>
+        <v>1577.977148033053</v>
       </c>
       <c r="C3" t="n">
-        <v>102.971502279936</v>
+        <v>94.91216797355909</v>
       </c>
       <c r="D3" t="n">
-        <v>624.0796335232025</v>
+        <v>624.8186962570024</v>
       </c>
       <c r="E3" t="n">
-        <v>1922.11626270909</v>
+        <v>1800.860080385952</v>
       </c>
       <c r="F3" t="n">
-        <v>164.7389718302901</v>
+        <v>157.6633698583571</v>
       </c>
       <c r="G3" t="n">
-        <v>76.85834877850012</v>
+        <v>71.1537603494169</v>
       </c>
     </row>
     <row r="4">
@@ -817,22 +817,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5461.562668262588</v>
+        <v>5470.658080929979</v>
       </c>
       <c r="C16" t="n">
-        <v>999.1907108853777</v>
+        <v>991.1313765790007</v>
       </c>
       <c r="D16" t="n">
-        <v>3588.727622308071</v>
+        <v>3589.466685041871</v>
       </c>
       <c r="E16" t="n">
-        <v>8251.716498607366</v>
+        <v>8130.460316284229</v>
       </c>
       <c r="F16" t="n">
-        <v>1651.920136111785</v>
+        <v>1644.844534139853</v>
       </c>
       <c r="G16" t="n">
-        <v>100.7969442243966</v>
+        <v>95.09235579531342</v>
       </c>
     </row>
   </sheetData>
